--- a/src/main/resources/static/ABC.xlsx
+++ b/src/main/resources/static/ABC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hieux\Desktop\Projects\src\main\resources\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5D7CF8D-1C1B-45A6-988E-F600CDD4EFBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1696F48-7B1E-4F60-91E3-AEEF0A47E670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{71050258-D013-4370-AEE7-AC2797CFA723}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="125">
   <si>
     <t>Thông tin chung</t>
   </si>
@@ -80,9 +80,6 @@
     <t>Mục đích</t>
   </si>
   <si>
-    <t>Loại định mức tài sản</t>
-  </si>
-  <si>
     <t>Mô tả</t>
   </si>
   <si>
@@ -401,7 +398,19 @@
     <t>Số tháng trích khấu hao</t>
   </si>
   <si>
-    <t>Giá trị lũy kế còn lại(*)</t>
+    <t>Còn lại</t>
+  </si>
+  <si>
+    <t>Thời gian trích khấu hao tối thiểu</t>
+  </si>
+  <si>
+    <t>Thời gian trích khấu hao tối đa</t>
+  </si>
+  <si>
+    <t>Lũy kế (*)</t>
+  </si>
+  <si>
+    <t>Giá trị còn lại</t>
   </si>
 </sst>
 </file>
@@ -410,14 +419,6 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -448,6 +449,13 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="23">
     <fill>
@@ -753,213 +761,222 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1296,325 +1313,325 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89576DAF-DCE1-420F-8F21-F841FF9B3DFA}">
-  <dimension ref="A1:EK3"/>
+  <dimension ref="A1:EM3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:141" x14ac:dyDescent="0.25">
-      <c r="A1" s="53" t="s">
+    <row r="1" spans="1:143" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
-      <c r="M1" s="54"/>
-      <c r="N1" s="54"/>
-      <c r="O1" s="54"/>
-      <c r="P1" s="55"/>
-      <c r="Q1" s="56" t="s">
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="57"/>
+      <c r="L1" s="57"/>
+      <c r="M1" s="57"/>
+      <c r="N1" s="57"/>
+      <c r="O1" s="58"/>
+      <c r="P1" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="R1" s="57"/>
-      <c r="S1" s="57"/>
-      <c r="T1" s="57"/>
-      <c r="U1" s="57"/>
-      <c r="V1" s="57"/>
-      <c r="W1" s="57"/>
-      <c r="X1" s="57"/>
-      <c r="Y1" s="57"/>
-      <c r="Z1" s="57"/>
-      <c r="AA1" s="57"/>
-      <c r="AB1" s="57"/>
-      <c r="AC1" s="57"/>
-      <c r="AD1" s="57"/>
-      <c r="AE1" s="57"/>
-      <c r="AF1" s="57"/>
-      <c r="AG1" s="57"/>
-      <c r="AH1" s="57"/>
-      <c r="AI1" s="57"/>
-      <c r="AJ1" s="57"/>
-      <c r="AK1" s="57"/>
-      <c r="AL1" s="57"/>
-      <c r="AM1" s="57"/>
-      <c r="AN1" s="57"/>
-      <c r="AO1" s="57"/>
-      <c r="AP1" s="57"/>
-      <c r="AQ1" s="57"/>
-      <c r="AR1" s="57"/>
-      <c r="AS1" s="57"/>
-      <c r="AT1" s="57"/>
-      <c r="AU1" s="57"/>
-      <c r="AV1" s="57"/>
-      <c r="AW1" s="57"/>
-      <c r="AX1" s="57"/>
-      <c r="AY1" s="57"/>
-      <c r="AZ1" s="57"/>
-      <c r="BA1" s="57"/>
-      <c r="BB1" s="57"/>
-      <c r="BC1" s="57"/>
-      <c r="BD1" s="57"/>
-      <c r="BE1" s="57"/>
-      <c r="BF1" s="57"/>
-      <c r="BG1" s="57"/>
-      <c r="BH1" s="57"/>
-      <c r="BI1" s="57"/>
-      <c r="BJ1" s="57"/>
-      <c r="BK1" s="57"/>
-      <c r="BL1" s="57"/>
-      <c r="BM1" s="57"/>
-      <c r="BN1" s="57"/>
-      <c r="BO1" s="57"/>
-      <c r="BP1" s="57"/>
-      <c r="BQ1" s="57"/>
-      <c r="BR1" s="57"/>
-      <c r="BS1" s="57"/>
-      <c r="BT1" s="57"/>
-      <c r="BU1" s="57"/>
-      <c r="BV1" s="57"/>
-      <c r="BW1" s="57"/>
-      <c r="BX1" s="57"/>
-      <c r="BY1" s="57"/>
-      <c r="BZ1" s="57"/>
-      <c r="CA1" s="57"/>
-      <c r="CB1" s="57"/>
-      <c r="CC1" s="57"/>
-      <c r="CD1" s="57"/>
-      <c r="CE1" s="57"/>
-      <c r="CF1" s="57"/>
-      <c r="CG1" s="57"/>
-      <c r="CH1" s="57"/>
-      <c r="CI1" s="57"/>
-      <c r="CJ1" s="57"/>
-      <c r="CK1" s="57"/>
-      <c r="CL1" s="57"/>
-      <c r="CM1" s="57"/>
-      <c r="CN1" s="58"/>
-      <c r="CO1" s="59" t="s">
+      <c r="Q1" s="71"/>
+      <c r="R1" s="71"/>
+      <c r="S1" s="71"/>
+      <c r="T1" s="71"/>
+      <c r="U1" s="71"/>
+      <c r="V1" s="71"/>
+      <c r="W1" s="71"/>
+      <c r="X1" s="71"/>
+      <c r="Y1" s="71"/>
+      <c r="Z1" s="71"/>
+      <c r="AA1" s="71"/>
+      <c r="AB1" s="71"/>
+      <c r="AC1" s="71"/>
+      <c r="AD1" s="71"/>
+      <c r="AE1" s="71"/>
+      <c r="AF1" s="71"/>
+      <c r="AG1" s="71"/>
+      <c r="AH1" s="71"/>
+      <c r="AI1" s="71"/>
+      <c r="AJ1" s="71"/>
+      <c r="AK1" s="71"/>
+      <c r="AL1" s="71"/>
+      <c r="AM1" s="71"/>
+      <c r="AN1" s="71"/>
+      <c r="AO1" s="71"/>
+      <c r="AP1" s="71"/>
+      <c r="AQ1" s="71"/>
+      <c r="AR1" s="71"/>
+      <c r="AS1" s="71"/>
+      <c r="AT1" s="71"/>
+      <c r="AU1" s="71"/>
+      <c r="AV1" s="71"/>
+      <c r="AW1" s="71"/>
+      <c r="AX1" s="71"/>
+      <c r="AY1" s="71"/>
+      <c r="AZ1" s="71"/>
+      <c r="BA1" s="71"/>
+      <c r="BB1" s="71"/>
+      <c r="BC1" s="71"/>
+      <c r="BD1" s="71"/>
+      <c r="BE1" s="71"/>
+      <c r="BF1" s="71"/>
+      <c r="BG1" s="71"/>
+      <c r="BH1" s="71"/>
+      <c r="BI1" s="71"/>
+      <c r="BJ1" s="71"/>
+      <c r="BK1" s="71"/>
+      <c r="BL1" s="71"/>
+      <c r="BM1" s="71"/>
+      <c r="BN1" s="71"/>
+      <c r="BO1" s="71"/>
+      <c r="BP1" s="71"/>
+      <c r="BQ1" s="71"/>
+      <c r="BR1" s="71"/>
+      <c r="BS1" s="71"/>
+      <c r="BT1" s="71"/>
+      <c r="BU1" s="71"/>
+      <c r="BV1" s="71"/>
+      <c r="BW1" s="71"/>
+      <c r="BX1" s="71"/>
+      <c r="BY1" s="71"/>
+      <c r="BZ1" s="71"/>
+      <c r="CA1" s="71"/>
+      <c r="CB1" s="71"/>
+      <c r="CC1" s="71"/>
+      <c r="CD1" s="71"/>
+      <c r="CE1" s="71"/>
+      <c r="CF1" s="71"/>
+      <c r="CG1" s="71"/>
+      <c r="CH1" s="71"/>
+      <c r="CI1" s="71"/>
+      <c r="CJ1" s="71"/>
+      <c r="CK1" s="71"/>
+      <c r="CL1" s="71"/>
+      <c r="CM1" s="72"/>
+      <c r="CN1" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="CP1" s="60"/>
-      <c r="CQ1" s="60"/>
-      <c r="CR1" s="60"/>
-      <c r="CS1" s="60"/>
-      <c r="CT1" s="60"/>
-      <c r="CU1" s="60"/>
-      <c r="CV1" s="61"/>
-      <c r="CW1" s="65" t="s">
+      <c r="CO1" s="65"/>
+      <c r="CP1" s="65"/>
+      <c r="CQ1" s="65"/>
+      <c r="CR1" s="65"/>
+      <c r="CS1" s="65"/>
+      <c r="CT1" s="65"/>
+      <c r="CU1" s="66"/>
+      <c r="CV1" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="CX1" s="66"/>
-      <c r="CY1" s="66"/>
-      <c r="CZ1" s="66"/>
-      <c r="DA1" s="66"/>
-      <c r="DB1" s="66"/>
-      <c r="DC1" s="66"/>
-      <c r="DD1" s="66"/>
-      <c r="DE1" s="66"/>
-      <c r="DF1" s="66"/>
-      <c r="DG1" s="66"/>
-      <c r="DH1" s="66"/>
-      <c r="DI1" s="66"/>
-      <c r="DJ1" s="66"/>
-      <c r="DK1" s="66"/>
-      <c r="DL1" s="66"/>
-      <c r="DM1" s="66"/>
-      <c r="DN1" s="66"/>
-      <c r="DO1" s="66"/>
-      <c r="DP1" s="66"/>
-      <c r="DQ1" s="66"/>
-      <c r="DR1" s="66"/>
-      <c r="DS1" s="66"/>
-      <c r="DT1" s="66"/>
-      <c r="DU1" s="66"/>
-      <c r="DV1" s="66"/>
-      <c r="DW1" s="66"/>
-      <c r="DX1" s="66"/>
-      <c r="DY1" s="67"/>
-      <c r="DZ1" s="68" t="s">
+      <c r="CW1" s="62"/>
+      <c r="CX1" s="62"/>
+      <c r="CY1" s="62"/>
+      <c r="CZ1" s="62"/>
+      <c r="DA1" s="62"/>
+      <c r="DB1" s="62"/>
+      <c r="DC1" s="62"/>
+      <c r="DD1" s="62"/>
+      <c r="DE1" s="62"/>
+      <c r="DF1" s="62"/>
+      <c r="DG1" s="62"/>
+      <c r="DH1" s="62"/>
+      <c r="DI1" s="62"/>
+      <c r="DJ1" s="62"/>
+      <c r="DK1" s="62"/>
+      <c r="DL1" s="62"/>
+      <c r="DM1" s="62"/>
+      <c r="DN1" s="62"/>
+      <c r="DO1" s="62"/>
+      <c r="DP1" s="62"/>
+      <c r="DQ1" s="62"/>
+      <c r="DR1" s="62"/>
+      <c r="DS1" s="62"/>
+      <c r="DT1" s="62"/>
+      <c r="DU1" s="62"/>
+      <c r="DV1" s="62"/>
+      <c r="DW1" s="62"/>
+      <c r="DX1" s="63"/>
+      <c r="DY1" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="EA1" s="69"/>
-      <c r="EB1" s="69"/>
-      <c r="EC1" s="69"/>
-      <c r="ED1" s="69"/>
-      <c r="EE1" s="69"/>
-      <c r="EF1" s="69"/>
-      <c r="EG1" s="69"/>
-      <c r="EH1" s="69"/>
-      <c r="EI1" s="69"/>
-      <c r="EJ1" s="69"/>
-      <c r="EK1" s="69"/>
+      <c r="DZ1" s="60"/>
+      <c r="EA1" s="60"/>
+      <c r="EB1" s="60"/>
+      <c r="EC1" s="60"/>
+      <c r="ED1" s="60"/>
+      <c r="EE1" s="60"/>
+      <c r="EF1" s="60"/>
+      <c r="EG1" s="60"/>
+      <c r="EH1" s="60"/>
+      <c r="EI1" s="60"/>
+      <c r="EJ1" s="60"/>
+      <c r="EK1" s="60"/>
+      <c r="EL1" s="60"/>
+      <c r="EM1" s="60"/>
     </row>
-    <row r="2" spans="1:141" x14ac:dyDescent="0.25">
-      <c r="A2" s="51" t="s">
+    <row r="2" spans="1:143" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="51" t="s">
+      <c r="B2" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="52" t="s">
+      <c r="C2" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="51" t="s">
+      <c r="D2" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="51" t="s">
+      <c r="E2" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="51" t="s">
+      <c r="F2" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="51" t="s">
+      <c r="G2" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="51" t="s">
+      <c r="H2" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="52" t="s">
+      <c r="I2" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="51" t="s">
+      <c r="J2" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="52" t="s">
+      <c r="K2" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="L2" s="51" t="s">
+      <c r="L2" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="M2" s="52" t="s">
+      <c r="M2" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="N2" s="51" t="s">
+      <c r="N2" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="O2" s="52" t="s">
+      <c r="O2" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="P2" s="52" t="s">
+      <c r="P2" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="Q2" s="32" t="s">
-        <v>21</v>
-      </c>
+      <c r="Q2" s="32"/>
       <c r="R2" s="32"/>
       <c r="S2" s="32"/>
       <c r="T2" s="32"/>
       <c r="U2" s="32"/>
       <c r="V2" s="32"/>
-      <c r="W2" s="32"/>
-      <c r="X2" s="45" t="s">
+      <c r="W2" s="48" t="s">
+        <v>21</v>
+      </c>
+      <c r="X2" s="48"/>
+      <c r="Y2" s="48"/>
+      <c r="Z2" s="48"/>
+      <c r="AA2" s="49" t="s">
         <v>22</v>
       </c>
-      <c r="Y2" s="45"/>
-      <c r="Z2" s="45"/>
-      <c r="AA2" s="45"/>
-      <c r="AB2" s="46" t="s">
+      <c r="AB2" s="49"/>
+      <c r="AC2" s="49"/>
+      <c r="AD2" s="49"/>
+      <c r="AE2" s="49"/>
+      <c r="AF2" s="49"/>
+      <c r="AG2" s="49"/>
+      <c r="AH2" s="49"/>
+      <c r="AI2" s="49"/>
+      <c r="AJ2" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="AC2" s="46"/>
-      <c r="AD2" s="46"/>
-      <c r="AE2" s="46"/>
-      <c r="AF2" s="46"/>
-      <c r="AG2" s="46"/>
-      <c r="AH2" s="46"/>
-      <c r="AI2" s="46"/>
-      <c r="AJ2" s="46"/>
-      <c r="AK2" s="47" t="s">
+      <c r="AK2" s="50"/>
+      <c r="AL2" s="50"/>
+      <c r="AM2" s="50"/>
+      <c r="AN2" s="50"/>
+      <c r="AO2" s="50"/>
+      <c r="AP2" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="AL2" s="47"/>
-      <c r="AM2" s="47"/>
-      <c r="AN2" s="47"/>
-      <c r="AO2" s="47"/>
-      <c r="AP2" s="47"/>
-      <c r="AQ2" s="48" t="s">
+      <c r="AQ2" s="51"/>
+      <c r="AR2" s="51"/>
+      <c r="AS2" s="51"/>
+      <c r="AT2" s="51"/>
+      <c r="AU2" s="51"/>
+      <c r="AV2" s="51"/>
+      <c r="AW2" s="51"/>
+      <c r="AX2" s="51"/>
+      <c r="AY2" s="51"/>
+      <c r="AZ2" s="51"/>
+      <c r="BA2" s="51"/>
+      <c r="BB2" s="51"/>
+      <c r="BC2" s="51"/>
+      <c r="BD2" s="51"/>
+      <c r="BE2" s="51"/>
+      <c r="BF2" s="51"/>
+      <c r="BG2" s="51"/>
+      <c r="BH2" s="51"/>
+      <c r="BI2" s="51"/>
+      <c r="BJ2" s="51"/>
+      <c r="BK2" s="51"/>
+      <c r="BL2" s="51"/>
+      <c r="BM2" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="AR2" s="48"/>
-      <c r="AS2" s="48"/>
-      <c r="AT2" s="48"/>
-      <c r="AU2" s="48"/>
-      <c r="AV2" s="48"/>
-      <c r="AW2" s="48"/>
-      <c r="AX2" s="48"/>
-      <c r="AY2" s="48"/>
-      <c r="AZ2" s="48"/>
-      <c r="BA2" s="48"/>
-      <c r="BB2" s="48"/>
-      <c r="BC2" s="48"/>
-      <c r="BD2" s="48"/>
-      <c r="BE2" s="48"/>
-      <c r="BF2" s="48"/>
-      <c r="BG2" s="48"/>
-      <c r="BH2" s="48"/>
-      <c r="BI2" s="48"/>
-      <c r="BJ2" s="48"/>
-      <c r="BK2" s="48"/>
-      <c r="BL2" s="48"/>
-      <c r="BM2" s="48"/>
-      <c r="BN2" s="49" t="s">
+      <c r="BN2" s="52"/>
+      <c r="BO2" s="52"/>
+      <c r="BP2" s="52"/>
+      <c r="BQ2" s="52"/>
+      <c r="BR2" s="52"/>
+      <c r="BS2" s="52"/>
+      <c r="BT2" s="52"/>
+      <c r="BU2" s="52"/>
+      <c r="BV2" s="52"/>
+      <c r="BW2" s="52"/>
+      <c r="BX2" s="52"/>
+      <c r="BY2" s="52"/>
+      <c r="BZ2" s="52"/>
+      <c r="CA2" s="52"/>
+      <c r="CB2" s="52"/>
+      <c r="CC2" s="52"/>
+      <c r="CD2" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="BO2" s="49"/>
-      <c r="BP2" s="49"/>
-      <c r="BQ2" s="49"/>
-      <c r="BR2" s="49"/>
-      <c r="BS2" s="49"/>
-      <c r="BT2" s="49"/>
-      <c r="BU2" s="49"/>
-      <c r="BV2" s="49"/>
-      <c r="BW2" s="49"/>
-      <c r="BX2" s="49"/>
-      <c r="BY2" s="49"/>
-      <c r="BZ2" s="49"/>
-      <c r="CA2" s="49"/>
-      <c r="CB2" s="49"/>
-      <c r="CC2" s="49"/>
-      <c r="CD2" s="49"/>
-      <c r="CE2" s="50" t="s">
+      <c r="CE2" s="45"/>
+      <c r="CF2" s="45"/>
+      <c r="CG2" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="CF2" s="50"/>
-      <c r="CG2" s="50"/>
-      <c r="CH2" s="32" t="s">
-        <v>28</v>
-      </c>
+      <c r="CH2" s="32"/>
       <c r="CI2" s="32"/>
       <c r="CJ2" s="32"/>
       <c r="CK2" s="32"/>
       <c r="CL2" s="32"/>
       <c r="CM2" s="32"/>
-      <c r="CN2" s="32"/>
-      <c r="CO2" s="62"/>
-      <c r="CP2" s="63"/>
-      <c r="CQ2" s="63"/>
-      <c r="CR2" s="63"/>
-      <c r="CS2" s="63"/>
-      <c r="CT2" s="63"/>
-      <c r="CU2" s="63"/>
-      <c r="CV2" s="64"/>
-      <c r="CW2" s="33" t="s">
+      <c r="CN2" s="67"/>
+      <c r="CO2" s="68"/>
+      <c r="CP2" s="68"/>
+      <c r="CQ2" s="68"/>
+      <c r="CR2" s="68"/>
+      <c r="CS2" s="68"/>
+      <c r="CT2" s="68"/>
+      <c r="CU2" s="69"/>
+      <c r="CV2" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="CW2" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="CX2" s="35" t="s">
-        <v>30</v>
-      </c>
+      <c r="CX2" s="36"/>
       <c r="CY2" s="36"/>
       <c r="CZ2" s="36"/>
       <c r="DA2" s="36"/>
-      <c r="DB2" s="36"/>
-      <c r="DC2" s="37"/>
-      <c r="DD2" s="38" t="s">
-        <v>31</v>
-      </c>
+      <c r="DB2" s="37"/>
+      <c r="DC2" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="DD2" s="38"/>
       <c r="DE2" s="38"/>
       <c r="DF2" s="38"/>
       <c r="DG2" s="38"/>
@@ -1623,10 +1640,10 @@
       <c r="DJ2" s="38"/>
       <c r="DK2" s="38"/>
       <c r="DL2" s="38"/>
-      <c r="DM2" s="38"/>
-      <c r="DN2" s="39" t="s">
-        <v>32</v>
-      </c>
+      <c r="DM2" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="DN2" s="40"/>
       <c r="DO2" s="40"/>
       <c r="DP2" s="40"/>
       <c r="DQ2" s="40"/>
@@ -1636,69 +1653,75 @@
       <c r="DU2" s="40"/>
       <c r="DV2" s="40"/>
       <c r="DW2" s="40"/>
-      <c r="DX2" s="40"/>
-      <c r="DY2" s="41"/>
-      <c r="DZ2" s="42" t="s">
+      <c r="DX2" s="41"/>
+      <c r="DY2" s="42" t="s">
         <v>0</v>
       </c>
+      <c r="DZ2" s="43"/>
       <c r="EA2" s="43"/>
-      <c r="EB2" s="43"/>
-      <c r="EC2" s="44"/>
-      <c r="ED2" s="26" t="s">
+      <c r="EB2" s="44"/>
+      <c r="EC2" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="ED2" s="27"/>
+      <c r="EE2" s="27"/>
+      <c r="EF2" s="28"/>
+      <c r="EG2" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="EE2" s="27"/>
-      <c r="EF2" s="27"/>
-      <c r="EG2" s="28"/>
-      <c r="EH2" s="29" t="s">
+      <c r="EH2" s="30"/>
+      <c r="EI2" s="31"/>
+      <c r="EJ2" s="25"/>
+      <c r="EK2" s="25"/>
+      <c r="EL2" s="55" t="s">
+        <v>120</v>
+      </c>
+      <c r="EM2" s="55"/>
+    </row>
+    <row r="3" spans="1:143" ht="90" x14ac:dyDescent="0.25">
+      <c r="A3" s="47"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="47"/>
+      <c r="K3" s="47"/>
+      <c r="L3" s="47"/>
+      <c r="M3" s="47"/>
+      <c r="N3" s="47"/>
+      <c r="O3" s="47"/>
+      <c r="P3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="EI2" s="30"/>
-      <c r="EJ2" s="31"/>
-      <c r="EK2" s="3"/>
-    </row>
-    <row r="3" spans="1:141" ht="90" x14ac:dyDescent="0.25">
-      <c r="A3" s="52"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="52"/>
-      <c r="K3" s="52"/>
-      <c r="L3" s="52"/>
-      <c r="M3" s="52"/>
-      <c r="N3" s="52"/>
-      <c r="O3" s="52"/>
-      <c r="P3" s="52"/>
-      <c r="Q3" s="4" t="s">
+      <c r="Q3" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="R3" s="4" t="s">
+      <c r="R3" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="S3" s="4" t="s">
+      <c r="S3" s="3" t="s">
         <v>37</v>
       </c>
       <c r="T3" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="U3" s="5" t="s">
+      <c r="U3" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="V3" s="5" t="s">
+      <c r="V3" s="4" t="s">
         <v>40</v>
       </c>
       <c r="W3" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="X3" s="6" t="s">
+      <c r="X3" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="Y3" s="6" t="s">
+      <c r="Y3" s="5" t="s">
         <v>43</v>
       </c>
       <c r="Z3" s="6" t="s">
@@ -1710,272 +1733,272 @@
       <c r="AB3" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="AC3" s="9" t="s">
+      <c r="AC3" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD3" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE3" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF3" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="AD3" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="AE3" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="AF3" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="AG3" s="10" t="s">
+      <c r="AG3" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="AH3" s="8" t="s">
+      <c r="AH3" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="AI3" s="8" t="s">
+      <c r="AI3" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="AJ3" s="8" t="s">
+      <c r="AJ3" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="AK3" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="AK3" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="AL3" s="12" t="s">
+      <c r="AL3" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="AM3" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="AM3" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="AN3" s="12" t="s">
+      <c r="AN3" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="AO3" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="AP3" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="AO3" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="AP3" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="AQ3" s="13" t="s">
+      <c r="AQ3" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="AR3" s="13" t="s">
+      <c r="AR3" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="AS3" s="13" t="s">
+      <c r="AS3" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="AT3" s="13" t="s">
+      <c r="AT3" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="AU3" s="13" t="s">
+      <c r="AU3" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="AV3" s="13" t="s">
+      <c r="AV3" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="AW3" s="13" t="s">
+      <c r="AW3" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="AX3" s="13" t="s">
+      <c r="AX3" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="AY3" s="13" t="s">
+      <c r="AY3" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="AZ3" s="13" t="s">
+      <c r="AZ3" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="BA3" s="13" t="s">
+      <c r="BA3" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="BB3" s="13" t="s">
-        <v>65</v>
+      <c r="BB3" s="12" t="s">
+        <v>37</v>
       </c>
       <c r="BC3" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="BD3" s="14" t="s">
+      <c r="BD3" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="BE3" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="BF3" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="BG3" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="BH3" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="BI3" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="BE3" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="BF3" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="BG3" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="BH3" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="BI3" s="13" t="s">
+      <c r="BJ3" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="BK3" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="BJ3" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="BK3" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="BL3" s="14" t="s">
+      <c r="BL3" s="13" t="s">
         <v>71</v>
       </c>
       <c r="BM3" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="BN3" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="BO3" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="BP3" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="BN3" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="BO3" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="BP3" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="BQ3" s="15" t="s">
+      <c r="BQ3" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="BR3" s="15" t="s">
+      <c r="BR3" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="BS3" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="BT3" s="15" t="s">
+      <c r="BS3" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="BT3" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="BU3" s="15" t="s">
-        <v>65</v>
+      <c r="BU3" s="14" t="s">
+        <v>37</v>
       </c>
       <c r="BV3" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="BW3" s="16" t="s">
+      <c r="BW3" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX3" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="BY3" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="BZ3" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="CA3" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="CB3" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="BX3" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="BY3" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="BZ3" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="CA3" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="CB3" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="CC3" s="16" t="s">
+      <c r="CC3" s="15" t="s">
         <v>40</v>
       </c>
       <c r="CD3" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="CE3" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="CF3" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="CG3" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="CH3" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="CE3" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="CF3" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="CG3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="CH3" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="CI3" s="4" t="s">
+      <c r="CI3" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="CJ3" s="4" t="s">
+      <c r="CJ3" s="3" t="s">
         <v>37</v>
       </c>
       <c r="CK3" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="CL3" s="5" t="s">
+      <c r="CL3" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="CM3" s="5" t="s">
+      <c r="CM3" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="CN3" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="CO3" s="18" t="s">
+      <c r="CN3" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="CO3" s="17" t="s">
         <v>74</v>
       </c>
       <c r="CP3" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="CQ3" s="19" t="s">
+      <c r="CQ3" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="CR3" s="19" t="s">
+      <c r="CR3" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="CS3" s="19" t="s">
+      <c r="CS3" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="CT3" s="19" t="s">
+      <c r="CT3" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="CU3" s="19" t="s">
+      <c r="CU3" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="CV3" s="19" t="s">
+      <c r="CV3" s="34"/>
+      <c r="CW3" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="CW3" s="34"/>
-      <c r="CX3" s="20" t="s">
+      <c r="CX3" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="CY3" s="20" t="s">
+      <c r="CY3" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="CZ3" s="20" t="s">
+      <c r="CZ3" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="DA3" s="20" t="s">
+      <c r="DA3" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="DB3" s="20" t="s">
+      <c r="DB3" s="19" t="s">
         <v>86</v>
       </c>
       <c r="DC3" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="DD3" s="21" t="s">
+      <c r="DD3" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="DE3" s="21" t="s">
+      <c r="DE3" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="DF3" s="21" t="s">
+      <c r="DF3" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="DG3" s="21" t="s">
+      <c r="DG3" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="DH3" s="21" t="s">
+      <c r="DH3" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="DI3" s="21" t="s">
+      <c r="DI3" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="DJ3" s="21" t="s">
+      <c r="DJ3" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="DK3" s="21" t="s">
+      <c r="DK3" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="DL3" s="21" t="s">
+      <c r="DL3" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="DM3" s="21" t="s">
+      <c r="DM3" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="DN3" s="1" t="s">
+      <c r="DN3" s="2" t="s">
         <v>98</v>
       </c>
       <c r="DO3" s="2" t="s">
@@ -2008,7 +2031,7 @@
       <c r="DX3" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="DY3" s="2" t="s">
+      <c r="DY3" s="21" t="s">
         <v>109</v>
       </c>
       <c r="DZ3" s="22" t="s">
@@ -2017,81 +2040,87 @@
       <c r="EA3" s="23" t="s">
         <v>111</v>
       </c>
-      <c r="EB3" s="24" t="s">
+      <c r="EB3" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="EC3" s="23" t="s">
+      <c r="EC3" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="ED3" s="25" t="s">
+      <c r="ED3" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="EE3" s="25" t="s">
+      <c r="EE3" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="EF3" s="25" t="s">
+      <c r="EF3" s="24" t="s">
         <v>116</v>
       </c>
-      <c r="EG3" s="25" t="s">
+      <c r="EG3" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="EH3" s="13" t="s">
+      <c r="EH3" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="EI3" s="13" t="s">
+      <c r="EI3" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="EJ3" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="EK3" s="23" t="s">
+      <c r="EJ3" s="12" t="s">
         <v>121</v>
+      </c>
+      <c r="EK3" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="EL3" s="54" t="s">
+        <v>123</v>
+      </c>
+      <c r="EM3" s="22" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="DZ1:EK1"/>
+    <mergeCell ref="EL2:EM2"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="E2:E3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="Q1:CN1"/>
-    <mergeCell ref="CO1:CV2"/>
-    <mergeCell ref="CW1:DY1"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="P1:CM1"/>
+    <mergeCell ref="CN1:CU2"/>
+    <mergeCell ref="CV1:DX1"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="CE2:CG2"/>
+    <mergeCell ref="DY1:EM1"/>
+    <mergeCell ref="CD2:CF2"/>
+    <mergeCell ref="K2:K3"/>
     <mergeCell ref="L2:L3"/>
     <mergeCell ref="M2:M3"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="O2:O3"/>
-    <mergeCell ref="P2:P3"/>
-    <mergeCell ref="Q2:W2"/>
-    <mergeCell ref="X2:AA2"/>
-    <mergeCell ref="AB2:AJ2"/>
-    <mergeCell ref="AK2:AP2"/>
-    <mergeCell ref="AQ2:BM2"/>
-    <mergeCell ref="BN2:CD2"/>
-    <mergeCell ref="ED2:EG2"/>
-    <mergeCell ref="EH2:EJ2"/>
-    <mergeCell ref="CH2:CN2"/>
-    <mergeCell ref="CW2:CW3"/>
-    <mergeCell ref="CX2:DC2"/>
-    <mergeCell ref="DD2:DM2"/>
-    <mergeCell ref="DN2:DY2"/>
-    <mergeCell ref="DZ2:EC2"/>
+    <mergeCell ref="P2:V2"/>
+    <mergeCell ref="W2:Z2"/>
+    <mergeCell ref="AA2:AI2"/>
+    <mergeCell ref="AJ2:AO2"/>
+    <mergeCell ref="AP2:BL2"/>
+    <mergeCell ref="BM2:CC2"/>
+    <mergeCell ref="EC2:EF2"/>
+    <mergeCell ref="EG2:EI2"/>
+    <mergeCell ref="CG2:CM2"/>
+    <mergeCell ref="CV2:CV3"/>
+    <mergeCell ref="CW2:DB2"/>
+    <mergeCell ref="DC2:DL2"/>
+    <mergeCell ref="DM2:DX2"/>
+    <mergeCell ref="DY2:EB2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="A3" xr:uid="{67F5E4F5-B409-41C6-864C-CF43979A1046}">
+    <dataValidation type="list" allowBlank="1" sqref="A3" xr:uid="{C5A41CF8-7064-47B6-B6AA-885D3C4F8E9C}">
       <formula1>"Stt5_Xeôtô,Stt6_Phươngtiệnvậntảikhác,Stt7_Máymócthiếtbị,Stt9_Tàisảncốđịnhhữuhìnhkhác,Stt10_Quyềnsửdụngđất,Stt8_Câylâunămsúcvậtlàmviệc,Stt4_Vậtkiếntrúc,Stt3_Nhàcôngtrìnhxâydựng"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B3" xr:uid="{F9D76196-5AD7-44F6-9758-D43A86A7CEAF}">
+    <dataValidation type="list" allowBlank="1" sqref="B3" xr:uid="{31FE8475-5B68-4106-8420-257EEA2EB006}">
       <formula1>INDIRECT($A3)</formula1>
     </dataValidation>
   </dataValidations>
